--- a/Others/Fredrick/AISS_Verification_Evidence_Log.xlsx
+++ b/Others/Fredrick/AISS_Verification_Evidence_Log.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Contrast Audit'!$A$1:$J$45</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Gate Register'!$A$1:$K$73</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Step Summary'!$A$1:$N$12</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Gate Register'!$A$1:$K$143</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Step Summary'!$A$1:$N$22</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1686" uniqueCount="726">
   <si>
     <t xml:space="preserve">AISS Verification Evidence Log</t>
   </si>
@@ -39,6 +39,12 @@
     <t xml:space="preserve">Executable answer to: "How are you checking after each AISS that the output meets the step requirements?"</t>
   </si>
   <si>
+    <t xml:space="preserve">Scope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steps 1-20 (both implementation batches). 142 gates.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Project</t>
   </si>
   <si>
@@ -84,7 +90,7 @@
     <t xml:space="preserve">Step Summary   - one row per atomic step, metric bands, derived completion status</t>
   </si>
   <si>
-    <t xml:space="preserve">Gate Register  - all 72 gates, each with the verbatim requirement it defends</t>
+    <t xml:space="preserve">Gate Register  - all 142 gates, each with the verbatim requirement it defends</t>
   </si>
   <si>
     <t xml:space="preserve">Contrast Audit - every colour pair and its measured WCAG ratio</t>
@@ -402,6 +408,177 @@
     <t xml:space="preserve">All rendered targets measured &gt;= 48dp across 3 device profiles</t>
   </si>
   <si>
+    <t xml:space="preserve">BPTR-0422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0422-A01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define Passive Failure Motion Curves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requirements Traceability Coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 of 8 declared motion requirements gated = 100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF-377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF-377-A01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set Progressive Stepper Transitions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location Accuracy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.0 - stepper motion declared in exactly one documented location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete / Not Complete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0128-A01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Establish Global Atomic Byt Micro-Interaction Boundaries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 of 7 gated = 100%; AtomicButton.build = 13 lines vs 20 budget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTMAC-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTMAC-014-A01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interactive Touch Target Standardization Engine Setup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0 - one documented path; 1 gate DEFERRED (double-tap telemetry)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSIVW-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSIVW-001-A01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement strict client-side Input Masking on all template text area entry portals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 of 13 CDEs have a mask and rule = 100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IS12-CSIVW-011-AS01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IS12-CSIVW-011-AS01-A01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setup character formatting filters across text entry boxes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset &amp; Component Discovery Completeness - Text entry box wrapper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90% of target assets confirmed present</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% of target assets confirmed present</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% (full inventory)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ValidatedInputField present; 13/13 CDEs covered = 100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IS02-CSIVW-005-AS01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IS02-CSIVW-005-AS01-A01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program dynamic inline error layouts to activate when input fields fail validation checks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset &amp; Component Discovery Completeness - Form validation directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forms/ present with inline_error, form_gate, field_validation = 100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0160-A01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code and isolate mobile compound fields into distinct, standalone UI components featuring strict 48x48dp touch targets.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field/Element Identification Accuracy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 of 13 compound parts identified and mapped to a CDE regex rule = 100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF-197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF-197-A01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developing the Safe Error-Handling UI Rollback Handler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Template Definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete - 9 of 9 failure categories have a jargon-free template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIEVR-033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIEVR-033-A01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build Multi-Step Guided Carousel Layout Stepper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 of 8 gated = 100%; CarouselStepper.build = 17 lines vs 20 budget</t>
+  </si>
+  <si>
     <t xml:space="preserve">TOTAL</t>
   </si>
   <si>
@@ -1099,6 +1276,636 @@
   </si>
   <si>
     <t xml:space="preserve">A 12dp icon renders at 12dp but is wrapped in a &gt;=48dp tap area, and long-press surfaces the detail tooltip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0422-G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #1: "Set animation duration (300ms)."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Failure duration is exactly 300ms and is the emphasized rung of the shared ladder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0422-G2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #2: "Define easing curve."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A failure curve is defined, is decelerating, and is distinct from the generic default</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0422-G3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #3: "Decide dimming intensity." + Poka-Yoke: "Animation physically locks surrounding UI until acknowledged."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dim opacity sits in a usable band and the UI-lock flag is on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0422-G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #4: "Set auto-scroll."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto-scroll is decided (enabled) and has a duration no slower than the failure animation itself</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0422-G5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Self-Chasing: "Failed element pulses continuously until resolved."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulse period and opacity bounds are defined and coherent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0422-G6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completion Measures: "Standardized CSS transitions defined." + What Standardized Must Be Done: "Motion and animation design tokens."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The duration ladder is strictly ascending, every curve is a real curve, and no interactive transition exceeds the 200ms ceiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0422-G7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common Library to Store: "Motion &amp; Animation System" -- tokens.json is the source of truth.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every motion constant in Dart matches tokens.json exactly (no drift)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0422-G8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atomic Reusability: "Wraps all compliance/validation failures." + Mobile-First UX Decision: "Motion draws eye to failure point on any screen."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Failure, stepper-enter, stepper-exit and standard each resolve to a distinct curve, so motion carries meaning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF-377-G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #1: "Define slide-in duration (200ms)."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slide-in is exactly 200ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF-377-G2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #2: "Define slide-out duration."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slide-out is defined, non-zero, and no slower than the slide-in so the outgoing step clears first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF-377-G3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #3: "Decide easing function."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter and exit have distinct curves, both well-formed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF-377-G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #4: "Respect reduced motion preferences." + UI Implementation: "prefers-reduced-motion media queries."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HabotMotionPolicy collapses every duration to zero and stops looping motion under MediaQuery.disableAnimations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF-377-G5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completion Measures: "Transitions feel instantaneous and fluid."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both stepper durations sit at or under the 200ms interactive ceiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF-377-G6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poka-Yoke: "Unmounts previous steps from DOM to prevent accidental back-edits."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After advancing, the previous step is gone from the tree -- its fields cannot be focused or edited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0128-G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #1: "Define global tokens forcing minimal tap-target area distributions." + Mobile-First UX: "minimum 48 x 48px." + UI: "absolute minimum safety padding boundary of 8px."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 48dp target and 8dp safety padding are tokens, and the button defaults to the safety padding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0128-G2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #2: "Build an abstract, pure AtomicButton component under 20 lines of total functional code."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AtomicButton.build is 20 executable lines or fewer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0128-G3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #3: "Code dynamic visual feedback systems simulating rapid interactive state states (active, focus, hover)."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every MD3 interaction state has a distinct, ordered state-layer opacity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0128-G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #4: "Implement performance-tuned passive touch listeners directly to eradicate 300ms mobile touch-click delays completely."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tap callback fires within a single frame of the gesture -- no delay is introduced by the design system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0128-G5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poka-Yoke: "compiler constraints instantly flag compile errors if a developer creates a clickable component without specifying explicit touch padding parameters."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">touchPadding is a REQUIRED constructor argument with a validating assert -- it cannot be omitted or set negative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0128-G6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Self-Chasing: "Runtime assertions write explicit warning flags if computed bounding client rectangles fall beneath target 48px." + Completion: "Lighthouse accessibility 100 on interactive target criteria."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 10dp glyph renders inside a target that clears 48dp plus the 8dp safety boundary, with zero audit violations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0128-G7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completion Measures: "Lighthouse accessibility checks scoring an absolute 100 on interactive target criteria."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every AtomicButton carries a required semantic label and an accurate enabled flag -- an unlabelled button cannot be built</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTMAC-014-G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decision to be Made Before Setup Step: "Establish if expanding hit boxes beyond visible component outlines is acceptable for small icons."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The decision is recorded as YES and the padding maths implements it -- a small glyph gains a transparent target rather than growing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTMAC-014-G2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #1: "Wrap all interactive components in protective padding zones matching minimum target dimensions."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Padding always resolves the glyph to at least the 48dp floor, for every size from 1dp up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTMAC-014-G3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #2: "Set default dimensions for icon actions to maintain structural usability."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three icon sizes are defined, ascending, all on the 4dp sub-baseline, and all below the touch floor (so padding always does the work)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTMAC-014-G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #3: "Configure clearance spaces around closely positioned items to avoid accidental double taps."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clearance is the 8dp token and the predicate rejects touching or overlapping targets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTMAC-014-G5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile-First UI Decision: "Ensure row items maintain distinct spacing separations to avoid tracking confusion." + Poka-Yoke: "The component compiler throws layout warnings if an asset's interactive region drops below required touch target dimensions."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three flush-packed buttons still keep at least 8dp between their visible glyphs, from their own padding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTMAC-014-G6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #4: "Test alignment grids against different device screen scale definitions."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 48dp target survives rasterisation at every device pixel ratio in the approved matrix, including the fractional 2.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTMAC-014-G7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completion Measures: "Average frequency of double tap corrections on closely packed selections (&lt;1%)." + Self-Chasing: "Telemetry tracking logs touch patterns."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field telemetry metric. This suite gates the geometric precondition (G5) but cannot produce a correction rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSIVW-001-G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #1: "Embed an alphanumeric keystroke filter inside the core text area component."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The alphanumeric mask admits letters, digits and space, and rejects everything else</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSIVW-001-G2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #2: "Configure strict regular expression rules to block unauthorized character sets."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every mask kind has a pattern, and the numeric masks genuinely exclude letters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSIVW-001-G3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #3: "Physically reject text pasted from clipboard arrays that exceeds defined field memory caps."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An over-cap paste is rejected outright, leaving the old value untouched -- not silently truncated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSIVW-001-G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poka-Yoke: "The text area physically drops any pasted input that contains non-ASCII formatting profiles."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-ASCII is dropped, and the characters that carry meaning are transliterated rather than deleted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSIVW-001-G5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IS12-CSIVW-011 Poka-Yoke: "Strip out trailing white spaces and weird symbols automatically from clipboard text when values are pasted."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A paste is trimmed on the right, but ordinary typing of a trailing space is left alone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSIVW-001-G6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setup Step Description: "Audit all template text area entry portals across the application to create a complete inventory." + Metric: Scope Coverage / Audit Completeness.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every CDE in the inventory resolves to a rule, and every rule carries a mask, a pattern, a keyboard type and a plain-language message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSIVW-001-G7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completion Measures: "Zero recorded layout overflows or broken text strings across standard testing devices." + Atomic Reusability: "StandardTextInputMask element."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A disallowed character never reaches application state -- it is filtered before the controller, not flagged afterwards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IS12-CSIVW-011-G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #2: "Restrict non-numeric keystrokes from mounting inside cost or dimension inputs."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost and quantity rules use numeric keyboards and reject letters at the pattern level too</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IS12-CSIVW-011-G2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #1: "Apply real-time input formatting layers to asset data form boxes."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every CDE rule carries a formatter stack, so formatting is applied as the user types rather than on submit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IS12-CSIVW-011-G3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What Standardized Must Be Done: "Display all text field validation messages using accessible text strings, never relying on color changes alone." (also WCAG 2.1 SC 1.4.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every failure produces a non-empty text message; no rule signals an error by colour alone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IS12-CSIVW-011-G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #4: "Unlock or freeze form confirmation keys based on field validation status."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The gate refuses submission while any registered field is invalid, and unlocks the moment every field passes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IS12-CSIVW-011-G5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Self-Chasing: "Fields recheck validation criteria the second an error is edited, clearing warnings quickly once values pass rules."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An error is only shown once the field has been touched, and clears as soon as the value passes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IS12-CSIVW-011-G6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metric: Asset &amp; Component Discovery Completeness -- "Text entry box wrapper component shared". Floor 90% of target assets confirmed present, Optimal 100%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The shared wrapper exists and covers 100% of declared CDEs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IS12-CSIVW-011-G7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile-First UI Decision: "Add quick-clear X icons inside mobile text boxes to wipe out inputs in one tap." + UI Decision: "Display standard clear helper text blocks directly beneath form rows."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helper text renders under the field, and a single tap on the labelled clear control empties it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IS02-CSIVW-005-G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #1: "Bind custom inline error components to the blur events of core entry inputs." + Completion Measures: "faulty inputs trigger immediate under-field red messages."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error appears only after blur, renders below the field, and clears as soon as the value passes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IS02-CSIVW-005-G2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decision to be Made Before Setup Step: "Select the precise text size parameters required for inline descriptive error messages."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The decision is recorded as bodySmall (12sp on a 16sp line) and comes from the existing type scale rather than a new value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IS02-CSIVW-005-G3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #2: "Lock message text strings to display in high-contrast red parameters."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The error colour is the audited scheme error token, and it clears the 4.5:1 floor against the surfaces it is drawn on, in both schemes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IS02-CSIVW-005-G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #3: "Program form frameworks to freeze submission actions if active errors are present." + Poka-Yoke: "Form submission actions remain physically locked until all active field errors are resolved."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A single outstanding error locks submission regardless of how many other fields pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IS02-CSIVW-005-G5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #4: "Run automated user boundary input tests to confirm clear error block display."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount, percentage and time rules accept their exact boundaries and reject one step outside, in both directions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IS02-CSIVW-005-G6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What Standardized Must Be Done: "All error text placement rules must adhere strictly to central UI rules."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">revealAllErrors surfaces every outstanding error at once rather than one per submit attempt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0160-G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What Standardized Must Be Done: "Global Regex mapping per CDE applied to mobile text fields." + Completion: `Invalid_Data_Type_Errors == 0`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every CDE has a regex rule -- the completion measure is unreachable if even one data type is unmapped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0160-G2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setup Step Description: "Identify all compound entry fields (e.g., split address blocks, combined date-time fields) in mobile views." + Metric: Field/Element Identification Accuracy (Floor 95, Optimal 99).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The compound-field inventory is declared as data, covers the examples the spec names, and every part resolves to a real CDE rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0160-G3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile-First UX Implementation: `inputmode="numeric"` -- "Contextual keyboard triggering for faster thumb typing."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numeric CDEs request a numeric keyboard; text CDEs do not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0160-G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile-First UI Decision: "Visual input masks (e.g., MM/DD/YYYY placeholders) inside the text field."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every CDE whose format is not self-evident carries a placeholder, and the date placeholders match their patterns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0160-G5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile-First UX Implementation: `autocomplete="off"`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autocomplete is off by default across every rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0160-G6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setup Step (Action): "isolate mobile compound fields into distinct, standalone UI components featuring strict 48x48dp touch targets."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The date-time compound stacks on a 320dp viewport and each part renders at least 48dp tall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPTR-0160-G7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Self-Chasing: "User cannot tap the submit button while the field is invalid, forcing them to fix their own typo instantly to proceed."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An address block with one bad part blocks the whole compound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF-197-G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setup Step Description AND Decision Before Setup Step (the sheet lists both): "Define standardized user-facing error text templates for common system validation rejections." + Metric: Template Definition = Complete (no partial credit).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every failure category has a template, each with a title, a body and a retry label -- an unmapped failure is impossible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF-197-G2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile-First UX Decision: "Ensure error text displays do not use technical code terms, keeping descriptions simple and clear."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No template contains any word from the forbidden-jargon list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF-197-G3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #2: "Configure error log scrubbers to remove sensitive backend code path variables from user-facing logs." + Poka-Yoke: "Catch-all code structures strip out server-specific error language automatically before messages reach the UI layer."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A realistic server trace is scrubbed of paths, URLs, IPs, tokens, stack frames, SQL and emails -- and the scrubber reports itself clean after</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF-197-G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #3: "Wire up UI state controllers to fall back to generic, helpful confirmation notes when processing anomalies occur."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classification maps real failure shapes to the right template, and an unrecognised error still lands on a human sentence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF-197-G5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile-First UI Decision: "Include an explicit, easy-to-tap retry button within error notification areas."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every retryable category offers a retry label, and the categories where retrying cannot help do not pretend it will</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF-197-G6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completion Measures: "Confirm through testing that simulated server crashes result in clean, friendly alerts rather than system code traces." + 4 Substeps #4: "reset input sections back to verified local baseline states upon transaction failure."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 500 with a full stack trace surfaces as the plain-language template with a retry control, the form is restored to baseline, and no path, IP, SQL or frame appears anywhere on screen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF-197-G7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atomic Reusability: "Ensure the error handling boundary can wrap any data-aware component layout."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The boundary wraps a plain ListView and, with no baseline, presents the template without claiming a rollback occurred</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIEVR-033-G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #1: "Define step configuration paths inside localized form state machines."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The machine exposes its steps, current index, first/last flags and progress as data, independent of any widget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIEVR-033-G2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #2: "Build an atomic horizontal stepper container under 20 lines of total functional code."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CarouselStepper.build is 20 executable lines or fewer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIEVR-033-G3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completion Measures: "Forms glide across steps cleanly in under 200ms."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both slide durations sit at or under 200ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIEVR-033-G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Substeps #4: "Code an integrated bottom layout progress dot row to show users their step counts instantly." + UI Decision: "Highlight active step states with clear visual accents."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three dots render with exactly one widened active dot, the announced step count updates on advance, and the card swaps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIEVR-033-G5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile-First UX Implementation: "Validate all inputs inside the current card before letting users slide to subsequent steps." + Self-Chasing: "validation errors block forward progress tracking loops across all form steps."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A step with an invalid field refuses to advance, allows retreat, and reveals its errors on the blocked attempt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIEVR-033-G6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poka-Yoke: "Saves entered inputs locally if an accidental view closure occurs, allowing users to resume entries instantly."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The draft survives on the machine and can be restored wholesale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIEVR-033-G7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UX Decision: "Keep navigation actions easy to access with distinct next and back buttons." + UI Implementation: "Automatically close system keyboards during slide transitions."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next is inert on an invalid step and active once it validates; Back on the first step is a safe no-op; focus is released on each transition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIEVR-033-G8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metric: Scope Coverage / Audit Completeness -- Optimal "100% of relevant items identified and logged in an inventory register."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every field named by every step is registered with the gate -- no step can gate on a field nobody tracks</t>
   </si>
   <si>
     <t xml:space="preserve">Scheme</t>
@@ -1907,7 +2714,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -1973,123 +2780,131 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="2"/>
+      <c r="A9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A10" s="3"/>
+      <c r="B10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
+      <c r="A11" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="B11" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3"/>
-      <c r="B12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="A13" s="3"/>
+      <c r="B13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
+      <c r="A14" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="B14" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3"/>
-      <c r="B16" s="2"/>
+      <c r="B16" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="A17" s="3"/>
+      <c r="B17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3"/>
+      <c r="A18" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="B18" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3"/>
-      <c r="B20" s="2"/>
+      <c r="B20" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="A21" s="3"/>
+      <c r="B21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3"/>
+      <c r="A22" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="B22" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3"/>
       <c r="B23" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3"/>
       <c r="B24" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3"/>
       <c r="B25" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3"/>
-      <c r="B26" s="2"/>
+      <c r="B26" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="A27" s="3"/>
+      <c r="B27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3"/>
+      <c r="A28" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="B28" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3"/>
+      <c r="B29" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2108,7 +2923,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -2126,46 +2941,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2173,28 +2988,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J2" s="5" t="n">
         <f aca="false">COUNTIF('Gate Register'!$D:$D,$C2)</f>
@@ -2213,7 +3028,7 @@
         <v>Not Complete</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2221,28 +3036,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J3" s="6" t="n">
         <f aca="false">COUNTIF('Gate Register'!$D:$D,$C3)</f>
@@ -2261,7 +3076,7 @@
         <v>Not Complete</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2269,28 +3084,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J4" s="5" t="n">
         <f aca="false">COUNTIF('Gate Register'!$D:$D,$C4)</f>
@@ -2309,7 +3124,7 @@
         <v>Not Complete</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2317,28 +3132,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J5" s="6" t="n">
         <f aca="false">COUNTIF('Gate Register'!$D:$D,$C5)</f>
@@ -2357,7 +3172,7 @@
         <v>Not Complete</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2365,28 +3180,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J6" s="5" t="n">
         <f aca="false">COUNTIF('Gate Register'!$D:$D,$C6)</f>
@@ -2405,7 +3220,7 @@
         <v>Not Complete</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2413,28 +3228,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J7" s="6" t="n">
         <f aca="false">COUNTIF('Gate Register'!$D:$D,$C7)</f>
@@ -2453,7 +3268,7 @@
         <v>Not Complete</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2461,28 +3276,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J8" s="5" t="n">
         <f aca="false">COUNTIF('Gate Register'!$D:$D,$C8)</f>
@@ -2501,7 +3316,7 @@
         <v>Not Complete</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2509,28 +3324,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J9" s="6" t="n">
         <f aca="false">COUNTIF('Gate Register'!$D:$D,$C9)</f>
@@ -2549,7 +3364,7 @@
         <v>Not Complete</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2557,28 +3372,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J10" s="5" t="n">
         <f aca="false">COUNTIF('Gate Register'!$D:$D,$C10)</f>
@@ -2597,7 +3412,7 @@
         <v>Not Complete</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2605,28 +3420,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H11" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>118</v>
-      </c>
       <c r="I11" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J11" s="6" t="n">
         <f aca="false">COUNTIF('Gate Register'!$D:$D,$C11)</f>
@@ -2645,41 +3460,521 @@
         <v>Not Complete</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>126</v>
+      </c>
       <c r="C12" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
+        <v>127</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>133</v>
+      </c>
       <c r="J12" s="5" t="n">
-        <f aca="false">SUM(J2:J11)</f>
-        <v>72</v>
+        <f aca="false">COUNTIF('Gate Register'!$D:$D,$C12)</f>
+        <v>8</v>
       </c>
       <c r="K12" s="5" t="n">
-        <f aca="false">SUM(K2:K11)</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS('Gate Register'!$D:$D,$C12,'Gate Register'!$I:$I,"DEFERRED")</f>
+        <v>0</v>
       </c>
       <c r="L12" s="5" t="n">
-        <f aca="false">SUM(L2:L11)</f>
+        <f aca="false">COUNTIFS('Gate Register'!$D:$D,$C12,'Gate Register'!$K:$K,"Pass")</f>
         <v>0</v>
       </c>
       <c r="M12" s="5" t="str">
-        <f aca="false">IF(L12=J12,"ALL COMPLETE","INCOMPLETE")</f>
+        <f aca="false">IF($J12=0,"Not Complete",IF($L12=$J12,"Complete",IF($L12=0,"Not Complete","Partial")))</f>
+        <v>Not Complete</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <f aca="false">COUNTIF('Gate Register'!$D:$D,$C13)</f>
+        <v>6</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <f aca="false">COUNTIFS('Gate Register'!$D:$D,$C13,'Gate Register'!$I:$I,"DEFERRED")</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <f aca="false">COUNTIFS('Gate Register'!$D:$D,$C13,'Gate Register'!$K:$K,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="6" t="str">
+        <f aca="false">IF($J13=0,"Not Complete",IF($L13=$J13,"Complete",IF($L13=0,"Not Complete","Partial")))</f>
+        <v>Not Complete</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <f aca="false">COUNTIF('Gate Register'!$D:$D,$C14)</f>
+        <v>7</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <f aca="false">COUNTIFS('Gate Register'!$D:$D,$C14,'Gate Register'!$I:$I,"DEFERRED")</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <f aca="false">COUNTIFS('Gate Register'!$D:$D,$C14,'Gate Register'!$K:$K,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="5" t="str">
+        <f aca="false">IF($J14=0,"Not Complete",IF($L14=$J14,"Complete",IF($L14=0,"Not Complete","Partial")))</f>
+        <v>Not Complete</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <f aca="false">COUNTIF('Gate Register'!$D:$D,$C15)</f>
+        <v>7</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <f aca="false">COUNTIFS('Gate Register'!$D:$D,$C15,'Gate Register'!$I:$I,"DEFERRED")</f>
+        <v>1</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <f aca="false">COUNTIFS('Gate Register'!$D:$D,$C15,'Gate Register'!$K:$K,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="6" t="str">
+        <f aca="false">IF($J15=0,"Not Complete",IF($L15=$J15,"Complete",IF($L15=0,"Not Complete","Partial")))</f>
+        <v>Not Complete</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <f aca="false">COUNTIF('Gate Register'!$D:$D,$C16)</f>
+        <v>7</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <f aca="false">COUNTIFS('Gate Register'!$D:$D,$C16,'Gate Register'!$I:$I,"DEFERRED")</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <f aca="false">COUNTIFS('Gate Register'!$D:$D,$C16,'Gate Register'!$K:$K,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="5" t="str">
+        <f aca="false">IF($J16=0,"Not Complete",IF($L16=$J16,"Complete",IF($L16=0,"Not Complete","Partial")))</f>
+        <v>Not Complete</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <f aca="false">COUNTIF('Gate Register'!$D:$D,$C17)</f>
+        <v>7</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <f aca="false">COUNTIFS('Gate Register'!$D:$D,$C17,'Gate Register'!$I:$I,"DEFERRED")</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <f aca="false">COUNTIFS('Gate Register'!$D:$D,$C17,'Gate Register'!$K:$K,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="6" t="str">
+        <f aca="false">IF($J17=0,"Not Complete",IF($L17=$J17,"Complete",IF($L17=0,"Not Complete","Partial")))</f>
+        <v>Not Complete</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <f aca="false">COUNTIF('Gate Register'!$D:$D,$C18)</f>
+        <v>6</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <f aca="false">COUNTIFS('Gate Register'!$D:$D,$C18,'Gate Register'!$I:$I,"DEFERRED")</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <f aca="false">COUNTIFS('Gate Register'!$D:$D,$C18,'Gate Register'!$K:$K,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="5" t="str">
+        <f aca="false">IF($J18=0,"Not Complete",IF($L18=$J18,"Complete",IF($L18=0,"Not Complete","Partial")))</f>
+        <v>Not Complete</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <f aca="false">COUNTIF('Gate Register'!$D:$D,$C19)</f>
+        <v>7</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <f aca="false">COUNTIFS('Gate Register'!$D:$D,$C19,'Gate Register'!$I:$I,"DEFERRED")</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="6" t="n">
+        <f aca="false">COUNTIFS('Gate Register'!$D:$D,$C19,'Gate Register'!$K:$K,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="6" t="str">
+        <f aca="false">IF($J19=0,"Not Complete",IF($L19=$J19,"Complete",IF($L19=0,"Not Complete","Partial")))</f>
+        <v>Not Complete</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <f aca="false">COUNTIF('Gate Register'!$D:$D,$C20)</f>
+        <v>7</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <f aca="false">COUNTIFS('Gate Register'!$D:$D,$C20,'Gate Register'!$I:$I,"DEFERRED")</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <f aca="false">COUNTIFS('Gate Register'!$D:$D,$C20,'Gate Register'!$K:$K,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="5" t="str">
+        <f aca="false">IF($J20=0,"Not Complete",IF($L20=$J20,"Complete",IF($L20=0,"Not Complete","Partial")))</f>
+        <v>Not Complete</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <f aca="false">COUNTIF('Gate Register'!$D:$D,$C21)</f>
+        <v>8</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <f aca="false">COUNTIFS('Gate Register'!$D:$D,$C21,'Gate Register'!$I:$I,"DEFERRED")</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="6" t="n">
+        <f aca="false">COUNTIFS('Gate Register'!$D:$D,$C21,'Gate Register'!$K:$K,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="6" t="str">
+        <f aca="false">IF($J21=0,"Not Complete",IF($L21=$J21,"Complete",IF($L21=0,"Not Complete","Partial")))</f>
+        <v>Not Complete</v>
+      </c>
+      <c r="N21" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5" t="n">
+        <f aca="false">SUM(J2:J21)</f>
+        <v>142</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <f aca="false">SUM(K2:K21)</f>
+        <v>3</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <f aca="false">SUM(L2:L21)</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="5" t="str">
+        <f aca="false">IF(L22=J22,"ALL COMPLETE","INCOMPLETE")</f>
         <v>INCOMPLETE</v>
       </c>
-      <c r="N12" s="5"/>
+      <c r="N22" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N12"/>
+  <autoFilter ref="A1:N22"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2696,7 +3991,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K143"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -2714,37 +4009,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>125</v>
+        <v>184</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>127</v>
+        <v>186</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>128</v>
+        <v>187</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>130</v>
+        <v>189</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>131</v>
+        <v>190</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>132</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2755,28 +4050,28 @@
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>134</v>
+        <v>193</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>135</v>
+        <v>194</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K2" s="7"/>
     </row>
@@ -2788,28 +4083,28 @@
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>139</v>
+        <v>198</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>140</v>
+        <v>199</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>141</v>
+        <v>200</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K3" s="7"/>
     </row>
@@ -2821,28 +4116,28 @@
         <v>1</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>143</v>
+        <v>202</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>144</v>
+        <v>203</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K4" s="7"/>
     </row>
@@ -2854,28 +4149,28 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>145</v>
+        <v>204</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>146</v>
+        <v>205</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>147</v>
+        <v>206</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K5" s="7"/>
     </row>
@@ -2887,28 +4182,28 @@
         <v>1</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>148</v>
+        <v>207</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>149</v>
+        <v>208</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>150</v>
+        <v>209</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K6" s="7"/>
     </row>
@@ -2920,28 +4215,28 @@
         <v>1</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>151</v>
+        <v>210</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>152</v>
+        <v>211</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>153</v>
+        <v>212</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K7" s="7"/>
     </row>
@@ -2953,28 +4248,28 @@
         <v>1</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>155</v>
+        <v>214</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>156</v>
+        <v>215</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>157</v>
+        <v>216</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K8" s="7"/>
     </row>
@@ -2986,28 +4281,28 @@
         <v>2</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>159</v>
+        <v>218</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>160</v>
+        <v>219</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>161</v>
+        <v>220</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K9" s="7"/>
     </row>
@@ -3019,28 +4314,28 @@
         <v>2</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>162</v>
+        <v>221</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>163</v>
+        <v>222</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>164</v>
+        <v>223</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>165</v>
+        <v>224</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K10" s="7"/>
     </row>
@@ -3052,28 +4347,28 @@
         <v>2</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>166</v>
+        <v>225</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>167</v>
+        <v>226</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>168</v>
+        <v>227</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K11" s="7"/>
     </row>
@@ -3085,28 +4380,28 @@
         <v>2</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>169</v>
+        <v>228</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>170</v>
+        <v>229</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>171</v>
+        <v>230</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K12" s="7"/>
     </row>
@@ -3118,28 +4413,28 @@
         <v>2</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>172</v>
+        <v>231</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>173</v>
+        <v>232</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>174</v>
+        <v>233</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K13" s="7"/>
     </row>
@@ -3151,28 +4446,28 @@
         <v>2</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>175</v>
+        <v>234</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>176</v>
+        <v>235</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>177</v>
+        <v>236</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>178</v>
+        <v>237</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K14" s="7"/>
     </row>
@@ -3184,28 +4479,28 @@
         <v>3</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>179</v>
+        <v>238</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>180</v>
+        <v>239</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>181</v>
+        <v>240</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K15" s="7"/>
     </row>
@@ -3217,28 +4512,28 @@
         <v>3</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>182</v>
+        <v>241</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>183</v>
+        <v>242</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>184</v>
+        <v>243</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K16" s="7"/>
     </row>
@@ -3250,28 +4545,28 @@
         <v>3</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>185</v>
+        <v>244</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>186</v>
+        <v>245</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>187</v>
+        <v>246</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>165</v>
+        <v>224</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K17" s="7"/>
     </row>
@@ -3283,28 +4578,28 @@
         <v>3</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>188</v>
+        <v>247</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>189</v>
+        <v>248</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>190</v>
+        <v>249</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>165</v>
+        <v>224</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K18" s="7"/>
     </row>
@@ -3316,28 +4611,28 @@
         <v>3</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>191</v>
+        <v>250</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>192</v>
+        <v>251</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>193</v>
+        <v>252</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K19" s="7"/>
     </row>
@@ -3349,28 +4644,28 @@
         <v>3</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>195</v>
+        <v>254</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>196</v>
+        <v>255</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>165</v>
+        <v>224</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K20" s="7"/>
     </row>
@@ -3382,28 +4677,28 @@
         <v>3</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E21" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J21" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="K21" s="7"/>
     </row>
@@ -3415,28 +4710,28 @@
         <v>3</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>200</v>
+        <v>259</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>201</v>
+        <v>260</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>202</v>
+        <v>261</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K22" s="7"/>
     </row>
@@ -3448,28 +4743,28 @@
         <v>3</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>203</v>
+        <v>262</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>204</v>
+        <v>263</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>205</v>
+        <v>264</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K23" s="7"/>
     </row>
@@ -3481,28 +4776,28 @@
         <v>4</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>206</v>
+        <v>265</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>207</v>
+        <v>266</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>208</v>
+        <v>267</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K24" s="7"/>
     </row>
@@ -3514,28 +4809,28 @@
         <v>4</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>209</v>
+        <v>268</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>210</v>
+        <v>269</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>211</v>
+        <v>270</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K25" s="7"/>
     </row>
@@ -3547,28 +4842,28 @@
         <v>4</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>212</v>
+        <v>271</v>
       </c>
       <c r="F26" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J26" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>154</v>
       </c>
       <c r="K26" s="7"/>
     </row>
@@ -3580,28 +4875,28 @@
         <v>4</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>215</v>
+        <v>274</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>216</v>
+        <v>275</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>217</v>
+        <v>276</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>165</v>
+        <v>224</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K27" s="7"/>
     </row>
@@ -3613,28 +4908,28 @@
         <v>4</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>218</v>
+        <v>277</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>219</v>
+        <v>278</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>220</v>
+        <v>279</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K28" s="7"/>
     </row>
@@ -3646,28 +4941,28 @@
         <v>4</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>221</v>
+        <v>280</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>222</v>
+        <v>281</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>223</v>
+        <v>282</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K29" s="7"/>
     </row>
@@ -3679,28 +4974,28 @@
         <v>4</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>225</v>
+        <v>284</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>226</v>
+        <v>285</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K30" s="7"/>
     </row>
@@ -3712,28 +5007,28 @@
         <v>4</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>227</v>
+        <v>286</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>228</v>
+        <v>287</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>229</v>
+        <v>288</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K31" s="7"/>
     </row>
@@ -3745,28 +5040,28 @@
         <v>5</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>230</v>
+        <v>289</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>231</v>
+        <v>290</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>232</v>
+        <v>291</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K32" s="7"/>
     </row>
@@ -3778,28 +5073,28 @@
         <v>5</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>233</v>
+        <v>292</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>234</v>
+        <v>293</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>235</v>
+        <v>294</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K33" s="7"/>
     </row>
@@ -3811,28 +5106,28 @@
         <v>5</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>236</v>
+        <v>295</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>237</v>
+        <v>296</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>238</v>
+        <v>297</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K34" s="7"/>
     </row>
@@ -3844,28 +5139,28 @@
         <v>5</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>240</v>
+        <v>299</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>241</v>
+        <v>300</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K35" s="7"/>
     </row>
@@ -3877,28 +5172,28 @@
         <v>5</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>242</v>
+        <v>301</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>243</v>
+        <v>302</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K36" s="7"/>
     </row>
@@ -3910,28 +5205,28 @@
         <v>5</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>245</v>
+        <v>304</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>246</v>
+        <v>305</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>247</v>
+        <v>306</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K37" s="7"/>
     </row>
@@ -3943,28 +5238,28 @@
         <v>5</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>248</v>
+        <v>307</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>249</v>
+        <v>308</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>250</v>
+        <v>309</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K38" s="7"/>
     </row>
@@ -3976,28 +5271,28 @@
         <v>5</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>252</v>
+        <v>311</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>253</v>
+        <v>312</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K39" s="7"/>
     </row>
@@ -4009,28 +5304,28 @@
         <v>6</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>256</v>
+        <v>315</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K40" s="7"/>
     </row>
@@ -4042,28 +5337,28 @@
         <v>6</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>259</v>
+        <v>318</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>260</v>
+        <v>319</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K41" s="8"/>
     </row>
@@ -4075,28 +5370,28 @@
         <v>6</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>262</v>
+        <v>321</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K42" s="7"/>
     </row>
@@ -4108,28 +5403,28 @@
         <v>6</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>266</v>
+        <v>325</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K43" s="7"/>
     </row>
@@ -4141,28 +5436,28 @@
         <v>6</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>267</v>
+        <v>326</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>268</v>
+        <v>327</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>269</v>
+        <v>328</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K44" s="7"/>
     </row>
@@ -4174,28 +5469,28 @@
         <v>6</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>270</v>
+        <v>329</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>271</v>
+        <v>330</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>272</v>
+        <v>331</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K45" s="7"/>
     </row>
@@ -4207,28 +5502,28 @@
         <v>6</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>273</v>
+        <v>332</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>274</v>
+        <v>333</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>275</v>
+        <v>334</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>260</v>
+        <v>319</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K46" s="8"/>
     </row>
@@ -4240,28 +5535,28 @@
         <v>7</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>276</v>
+        <v>335</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>277</v>
+        <v>336</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>278</v>
+        <v>337</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K47" s="7"/>
     </row>
@@ -4273,28 +5568,28 @@
         <v>7</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>279</v>
+        <v>338</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>280</v>
+        <v>339</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>281</v>
+        <v>340</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K48" s="7"/>
     </row>
@@ -4306,28 +5601,28 @@
         <v>7</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>282</v>
+        <v>341</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>283</v>
+        <v>342</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>284</v>
+        <v>343</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K49" s="7"/>
     </row>
@@ -4339,28 +5634,28 @@
         <v>7</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>285</v>
+        <v>344</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>286</v>
+        <v>345</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>287</v>
+        <v>346</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K50" s="7"/>
     </row>
@@ -4372,28 +5667,28 @@
         <v>7</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>288</v>
+        <v>347</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>289</v>
+        <v>348</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>290</v>
+        <v>349</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K51" s="7"/>
     </row>
@@ -4405,28 +5700,28 @@
         <v>7</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>291</v>
+        <v>350</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>292</v>
+        <v>351</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>293</v>
+        <v>352</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K52" s="7"/>
     </row>
@@ -4438,28 +5733,28 @@
         <v>7</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>294</v>
+        <v>353</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>295</v>
+        <v>354</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>296</v>
+        <v>355</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K53" s="7"/>
     </row>
@@ -4471,28 +5766,28 @@
         <v>8</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>297</v>
+        <v>356</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>298</v>
+        <v>357</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>299</v>
+        <v>358</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K54" s="7"/>
     </row>
@@ -4504,28 +5799,28 @@
         <v>8</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>300</v>
+        <v>359</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>301</v>
+        <v>360</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>302</v>
+        <v>361</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K55" s="7"/>
     </row>
@@ -4537,28 +5832,28 @@
         <v>8</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>303</v>
+        <v>362</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>304</v>
+        <v>363</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>305</v>
+        <v>364</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K56" s="7"/>
     </row>
@@ -4570,28 +5865,28 @@
         <v>8</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>306</v>
+        <v>365</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>307</v>
+        <v>366</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>308</v>
+        <v>367</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K57" s="7"/>
     </row>
@@ -4603,28 +5898,28 @@
         <v>8</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>309</v>
+        <v>368</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>310</v>
+        <v>369</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>311</v>
+        <v>370</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K58" s="7"/>
     </row>
@@ -4636,28 +5931,28 @@
         <v>8</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>312</v>
+        <v>371</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>313</v>
+        <v>372</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>314</v>
+        <v>373</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K59" s="7"/>
     </row>
@@ -4669,28 +5964,28 @@
         <v>9</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>316</v>
+        <v>375</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>317</v>
+        <v>376</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K60" s="7"/>
     </row>
@@ -4702,28 +5997,28 @@
         <v>9</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>318</v>
+        <v>377</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>319</v>
+        <v>378</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>320</v>
+        <v>379</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K61" s="7"/>
     </row>
@@ -4735,28 +6030,28 @@
         <v>9</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>321</v>
+        <v>380</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>323</v>
+        <v>382</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K62" s="7"/>
     </row>
@@ -4768,28 +6063,28 @@
         <v>9</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>324</v>
+        <v>383</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>325</v>
+        <v>384</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>326</v>
+        <v>385</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K63" s="7"/>
     </row>
@@ -4801,28 +6096,28 @@
         <v>9</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>327</v>
+        <v>386</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>328</v>
+        <v>387</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>329</v>
+        <v>388</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K64" s="7"/>
     </row>
@@ -4834,28 +6129,28 @@
         <v>9</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>330</v>
+        <v>389</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>331</v>
+        <v>390</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>332</v>
+        <v>391</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K65" s="7"/>
     </row>
@@ -4867,28 +6162,28 @@
         <v>9</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>333</v>
+        <v>392</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>334</v>
+        <v>393</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>335</v>
+        <v>394</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K66" s="7"/>
     </row>
@@ -4900,28 +6195,28 @@
         <v>10</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>336</v>
+        <v>395</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>337</v>
+        <v>396</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>338</v>
+        <v>397</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>165</v>
+        <v>224</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K67" s="7"/>
     </row>
@@ -4933,28 +6228,28 @@
         <v>10</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>339</v>
+        <v>398</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>340</v>
+        <v>399</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>341</v>
+        <v>400</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>165</v>
+        <v>224</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K68" s="7"/>
     </row>
@@ -4966,28 +6261,28 @@
         <v>10</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>342</v>
+        <v>401</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>343</v>
+        <v>402</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>344</v>
+        <v>403</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K69" s="7"/>
     </row>
@@ -4999,28 +6294,28 @@
         <v>10</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>345</v>
+        <v>404</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>346</v>
+        <v>405</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>347</v>
+        <v>406</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="K70" s="7"/>
     </row>
@@ -5032,28 +6327,28 @@
         <v>10</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>348</v>
+        <v>407</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>349</v>
+        <v>408</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>350</v>
+        <v>409</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K71" s="7"/>
     </row>
@@ -5065,28 +6360,28 @@
         <v>10</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>351</v>
+        <v>410</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>352</v>
+        <v>411</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>353</v>
+        <v>412</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="K72" s="7"/>
     </row>
@@ -5098,35 +6393,2345 @@
         <v>10</v>
       </c>
       <c r="C73" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J73" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="K73" s="7"/>
+    </row>
+    <row r="74" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J74" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K74" s="7"/>
+    </row>
+    <row r="75" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J75" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K75" s="7"/>
+    </row>
+    <row r="76" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="H76" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J76" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K76" s="7"/>
+    </row>
+    <row r="77" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J77" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K77" s="7"/>
+    </row>
+    <row r="78" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J78" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K78" s="7"/>
+    </row>
+    <row r="79" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J79" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K79" s="7"/>
+    </row>
+    <row r="80" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J80" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K80" s="7"/>
+    </row>
+    <row r="81" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="F81" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J81" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K81" s="7"/>
+    </row>
+    <row r="82" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J82" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K82" s="7"/>
+    </row>
+    <row r="83" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J83" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K83" s="7"/>
+    </row>
+    <row r="84" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="H84" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J84" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K84" s="7"/>
+    </row>
+    <row r="85" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J85" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="K85" s="7"/>
+    </row>
+    <row r="86" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="H86" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J86" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K86" s="7"/>
+    </row>
+    <row r="87" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J87" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="K87" s="7"/>
+    </row>
+    <row r="88" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J88" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K88" s="7"/>
+    </row>
+    <row r="89" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J89" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K89" s="7"/>
+    </row>
+    <row r="90" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="H90" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I90" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J90" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K90" s="7"/>
+    </row>
+    <row r="91" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J91" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="K91" s="7"/>
+    </row>
+    <row r="92" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="H92" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J92" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K92" s="7"/>
+    </row>
+    <row r="93" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J93" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="K93" s="7"/>
+    </row>
+    <row r="94" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="H94" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I94" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J94" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="K94" s="7"/>
+    </row>
+    <row r="95" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I95" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J95" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K95" s="7"/>
+    </row>
+    <row r="96" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="H96" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="I96" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J96" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K96" s="7"/>
+    </row>
+    <row r="97" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="I97" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J97" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K97" s="7"/>
+    </row>
+    <row r="98" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="H98" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I98" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J98" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K98" s="7"/>
+    </row>
+    <row r="99" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="6" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I99" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J99" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="K99" s="7"/>
+    </row>
+    <row r="100" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="H100" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="I100" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J100" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K100" s="7"/>
+    </row>
+    <row r="101" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="G101" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="H101" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="I101" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="J101" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="K101" s="8"/>
+    </row>
+    <row r="102" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="H102" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I102" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J102" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K102" s="7"/>
+    </row>
+    <row r="103" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I103" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J103" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K103" s="7"/>
+    </row>
+    <row r="104" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="5" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="H104" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I104" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J104" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K104" s="7"/>
+    </row>
+    <row r="105" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I105" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J105" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K105" s="7"/>
+    </row>
+    <row r="106" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="H106" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I106" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J106" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K106" s="7"/>
+    </row>
+    <row r="107" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="G107" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="H107" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I107" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J107" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K107" s="7"/>
+    </row>
+    <row r="108" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="G108" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="H108" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I108" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J108" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="K108" s="7"/>
+    </row>
+    <row r="109" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="G109" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="H109" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I109" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J109" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K109" s="7"/>
+    </row>
+    <row r="110" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="F110" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="H110" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I110" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J110" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="K110" s="7"/>
+    </row>
+    <row r="111" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="F111" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="G111" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="H111" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I111" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J111" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K111" s="7"/>
+    </row>
+    <row r="112" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="H112" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I112" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J112" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K112" s="7"/>
+    </row>
+    <row r="113" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="6" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E113" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="F113" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="G113" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="H113" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I113" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J113" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K113" s="7"/>
+    </row>
+    <row r="114" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="F114" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="H114" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I114" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J114" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K114" s="7"/>
+    </row>
+    <row r="115" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="6" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E115" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="G115" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="H115" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="I115" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J115" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="K115" s="7"/>
+    </row>
+    <row r="116" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="H116" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="I116" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J116" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="K116" s="7"/>
+    </row>
+    <row r="117" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="6" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="G117" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="H117" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I117" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J117" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K117" s="7"/>
+    </row>
+    <row r="118" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="H118" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="I118" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J118" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K118" s="7"/>
+    </row>
+    <row r="119" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="6" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="G119" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="H119" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I119" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J119" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K119" s="7"/>
+    </row>
+    <row r="120" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="H120" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I120" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J120" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="K120" s="7"/>
+    </row>
+    <row r="121" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="D73" s="6" t="s">
+      <c r="B121" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="G121" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="H121" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I121" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J121" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K121" s="7"/>
+    </row>
+    <row r="122" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="5" t="n">
         <v>121</v>
       </c>
-      <c r="E73" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="F73" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="G73" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="H73" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="I73" s="6" t="s">
+      <c r="B122" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E122" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="G122" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="H122" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I122" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J122" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K122" s="7"/>
+    </row>
+    <row r="123" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="6" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="G123" s="6" t="s">
+        <v>565</v>
+      </c>
+      <c r="H123" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I123" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J123" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K123" s="7"/>
+    </row>
+    <row r="124" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="G124" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="H124" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I124" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J124" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K124" s="7"/>
+    </row>
+    <row r="125" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="6" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="G125" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="H125" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I125" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J125" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K125" s="7"/>
+    </row>
+    <row r="126" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E126" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="F126" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="G126" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="H126" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I126" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J126" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K126" s="7"/>
+    </row>
+    <row r="127" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A127" s="6" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="F127" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="G127" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="H127" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="I127" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J127" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="K127" s="7"/>
+    </row>
+    <row r="128" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E128" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="F128" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="G128" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="H128" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I128" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J128" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K128" s="7"/>
+    </row>
+    <row r="129" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A129" s="6" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="E129" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="G129" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="H129" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I129" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J129" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K129" s="7"/>
+    </row>
+    <row r="130" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E130" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="F130" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="G130" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="H130" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I130" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J130" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K130" s="7"/>
+    </row>
+    <row r="131" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="F131" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="G131" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="H131" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I131" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J131" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K131" s="7"/>
+    </row>
+    <row r="132" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A132" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="F132" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="G132" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="H132" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I132" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J132" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K132" s="7"/>
+    </row>
+    <row r="133" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A133" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="E133" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="F133" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="G133" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="H133" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I133" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J133" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K133" s="7"/>
+    </row>
+    <row r="134" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="F134" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="G134" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="H134" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I134" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J134" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="K134" s="7"/>
+    </row>
+    <row r="135" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A135" s="6" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="E135" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="F135" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="G135" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="H135" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I135" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J135" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="K135" s="7"/>
+    </row>
+    <row r="136" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A136" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="F136" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="G136" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="H136" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I136" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J136" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="K136" s="7"/>
+    </row>
+    <row r="137" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A137" s="6" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="F137" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="G137" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="H137" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I137" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J137" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K137" s="7"/>
+    </row>
+    <row r="138" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A138" s="5" t="n">
         <v>137</v>
       </c>
-      <c r="J73" s="6" t="s">
+      <c r="B138" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E138" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="F138" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="G138" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="H138" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="I138" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J138" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K138" s="7"/>
+    </row>
+    <row r="139" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A139" s="6" t="n">
         <v>138</v>
       </c>
-      <c r="K73" s="7"/>
+      <c r="B139" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="F139" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="G139" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="H139" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="I139" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J139" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="K139" s="7"/>
+    </row>
+    <row r="140" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A140" s="5" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="G140" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="H140" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I140" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J140" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K140" s="7"/>
+    </row>
+    <row r="141" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A141" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="F141" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="G141" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="H141" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I141" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J141" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K141" s="7"/>
+    </row>
+    <row r="142" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A142" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="F142" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="H142" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I142" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J142" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="K142" s="7"/>
+    </row>
+    <row r="143" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A143" s="6" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="F143" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="G143" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="H143" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I143" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J143" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K143" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K73"/>
+  <autoFilter ref="A1:K143"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K73" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K143" type="list">
       <formula1>"Pass,Fail,Not Run"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5163,54 +8768,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>357</v>
+        <v>626</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>358</v>
+        <v>627</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>359</v>
+        <v>628</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>360</v>
+        <v>629</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>361</v>
+        <v>630</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>362</v>
+        <v>631</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>363</v>
+        <v>632</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>364</v>
+        <v>633</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>365</v>
+        <v>634</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>366</v>
+        <v>635</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>367</v>
+        <v>636</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>368</v>
+        <v>637</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>369</v>
+        <v>638</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>370</v>
+        <v>639</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>371</v>
+        <v>640</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G2" s="9" t="n">
         <v>8.06</v>
@@ -5219,7 +8824,7 @@
         <v>4.5</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J2" s="5" t="str">
         <f aca="false">IF(G2&gt;=H2,"PASS","FAIL")</f>
@@ -5228,22 +8833,22 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>367</v>
+        <v>636</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>374</v>
+        <v>643</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>375</v>
+        <v>644</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>376</v>
+        <v>645</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>377</v>
+        <v>646</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G3" s="10" t="n">
         <v>13.28</v>
@@ -5252,7 +8857,7 @@
         <v>4.5</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J3" s="6" t="str">
         <f aca="false">IF(G3&gt;=H3,"PASS","FAIL")</f>
@@ -5261,22 +8866,22 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>367</v>
+        <v>636</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>378</v>
+        <v>647</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>369</v>
+        <v>638</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>379</v>
+        <v>648</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>380</v>
+        <v>649</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G4" s="9" t="n">
         <v>8.46</v>
@@ -5285,7 +8890,7 @@
         <v>4.5</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J4" s="5" t="str">
         <f aca="false">IF(G4&gt;=H4,"PASS","FAIL")</f>
@@ -5294,22 +8899,22 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>367</v>
+        <v>636</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>381</v>
+        <v>650</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>382</v>
+        <v>651</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>383</v>
+        <v>652</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>384</v>
+        <v>653</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>13.14</v>
@@ -5318,7 +8923,7 @@
         <v>4.5</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J5" s="6" t="str">
         <f aca="false">IF(G5&gt;=H5,"PASS","FAIL")</f>
@@ -5327,22 +8932,22 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>367</v>
+        <v>636</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>385</v>
+        <v>654</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>369</v>
+        <v>638</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>386</v>
+        <v>655</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>387</v>
+        <v>656</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G6" s="9" t="n">
         <v>8.39</v>
@@ -5351,7 +8956,7 @@
         <v>4.5</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J6" s="5" t="str">
         <f aca="false">IF(G6&gt;=H6,"PASS","FAIL")</f>
@@ -5360,22 +8965,22 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>367</v>
+        <v>636</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>388</v>
+        <v>657</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>389</v>
+        <v>658</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>390</v>
+        <v>659</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>391</v>
+        <v>660</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>13.31</v>
@@ -5384,7 +8989,7 @@
         <v>4.5</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J7" s="6" t="str">
         <f aca="false">IF(G7&gt;=H7,"PASS","FAIL")</f>
@@ -5393,22 +8998,22 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>367</v>
+        <v>636</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>392</v>
+        <v>661</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>369</v>
+        <v>638</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>393</v>
+        <v>662</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>394</v>
+        <v>663</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>6.54</v>
@@ -5417,7 +9022,7 @@
         <v>4.5</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>395</v>
+        <v>664</v>
       </c>
       <c r="J8" s="5" t="str">
         <f aca="false">IF(G8&gt;=H8,"PASS","FAIL")</f>
@@ -5426,22 +9031,22 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>367</v>
+        <v>636</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>396</v>
+        <v>665</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>397</v>
+        <v>666</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>398</v>
+        <v>667</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>399</v>
+        <v>668</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>12.77</v>
@@ -5450,7 +9055,7 @@
         <v>4.5</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J9" s="6" t="str">
         <f aca="false">IF(G9&gt;=H9,"PASS","FAIL")</f>
@@ -5459,22 +9064,22 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>367</v>
+        <v>636</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>400</v>
+        <v>669</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>401</v>
+        <v>670</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>402</v>
+        <v>671</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>403</v>
+        <v>672</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>16.63</v>
@@ -5483,7 +9088,7 @@
         <v>4.5</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J10" s="5" t="str">
         <f aca="false">IF(G10&gt;=H10,"PASS","FAIL")</f>
@@ -5492,22 +9097,22 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>367</v>
+        <v>636</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>404</v>
+        <v>673</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>405</v>
+        <v>674</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>402</v>
+        <v>671</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>403</v>
+        <v>672</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>9.15</v>
@@ -5516,7 +9121,7 @@
         <v>4.5</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J11" s="6" t="str">
         <f aca="false">IF(G11&gt;=H11,"PASS","FAIL")</f>
@@ -5525,22 +9130,22 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>367</v>
+        <v>636</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>400</v>
+        <v>669</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>401</v>
+        <v>670</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>406</v>
+        <v>675</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>369</v>
+        <v>638</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>17.09</v>
@@ -5549,7 +9154,7 @@
         <v>4.5</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J12" s="5" t="str">
         <f aca="false">IF(G12&gt;=H12,"PASS","FAIL")</f>
@@ -5558,22 +9163,22 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>367</v>
+        <v>636</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>400</v>
+        <v>669</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>401</v>
+        <v>670</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>407</v>
+        <v>676</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>408</v>
+        <v>677</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>15.74</v>
@@ -5582,7 +9187,7 @@
         <v>4.5</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J13" s="6" t="str">
         <f aca="false">IF(G13&gt;=H13,"PASS","FAIL")</f>
@@ -5591,22 +9196,22 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>367</v>
+        <v>636</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>400</v>
+        <v>669</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>401</v>
+        <v>670</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>409</v>
+        <v>678</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>410</v>
+        <v>679</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>14.93</v>
@@ -5615,7 +9220,7 @@
         <v>4.5</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J14" s="5" t="str">
         <f aca="false">IF(G14&gt;=H14,"PASS","FAIL")</f>
@@ -5624,22 +9229,22 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>367</v>
+        <v>636</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>400</v>
+        <v>669</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>401</v>
+        <v>670</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>411</v>
+        <v>680</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>412</v>
+        <v>681</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G15" s="10" t="n">
         <v>14.14</v>
@@ -5648,7 +9253,7 @@
         <v>4.5</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J15" s="6" t="str">
         <f aca="false">IF(G15&gt;=H15,"PASS","FAIL")</f>
@@ -5657,22 +9262,22 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>367</v>
+        <v>636</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>400</v>
+        <v>669</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>401</v>
+        <v>670</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>413</v>
+        <v>682</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>414</v>
+        <v>683</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>13.39</v>
@@ -5681,7 +9286,7 @@
         <v>4.5</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J16" s="5" t="str">
         <f aca="false">IF(G16&gt;=H16,"PASS","FAIL")</f>
@@ -5690,22 +9295,22 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>367</v>
+        <v>636</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>415</v>
+        <v>684</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>416</v>
+        <v>685</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>417</v>
+        <v>686</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>418</v>
+        <v>687</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>11.6</v>
@@ -5714,7 +9319,7 @@
         <v>4.5</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J17" s="6" t="str">
         <f aca="false">IF(G17&gt;=H17,"PASS","FAIL")</f>
@@ -5723,22 +9328,22 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>367</v>
+        <v>636</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>419</v>
+        <v>688</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>420</v>
+        <v>689</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>402</v>
+        <v>671</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>403</v>
+        <v>672</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>421</v>
+        <v>690</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>4.36</v>
@@ -5747,7 +9352,7 @@
         <v>3</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>395</v>
+        <v>664</v>
       </c>
       <c r="J18" s="5" t="str">
         <f aca="false">IF(G18&gt;=H18,"PASS","FAIL")</f>
@@ -5756,22 +9361,22 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>367</v>
+        <v>636</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>370</v>
+        <v>639</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>371</v>
+        <v>640</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>402</v>
+        <v>671</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>403</v>
+        <v>672</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>421</v>
+        <v>690</v>
       </c>
       <c r="G19" s="10" t="n">
         <v>7.85</v>
@@ -5780,7 +9385,7 @@
         <v>3</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J19" s="6" t="str">
         <f aca="false">IF(G19&gt;=H19,"PASS","FAIL")</f>
@@ -5789,22 +9394,22 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>368</v>
+        <v>637</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>423</v>
+        <v>692</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>370</v>
+        <v>639</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>424</v>
+        <v>693</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>7.75</v>
@@ -5813,7 +9418,7 @@
         <v>4.5</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J20" s="5" t="str">
         <f aca="false">IF(G20&gt;=H20,"PASS","FAIL")</f>
@@ -5822,22 +9427,22 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>374</v>
+        <v>643</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>377</v>
+        <v>646</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>376</v>
+        <v>645</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>425</v>
+        <v>694</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G21" s="10" t="n">
         <v>7.25</v>
@@ -5846,7 +9451,7 @@
         <v>4.5</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J21" s="6" t="str">
         <f aca="false">IF(G21&gt;=H21,"PASS","FAIL")</f>
@@ -5855,22 +9460,22 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>378</v>
+        <v>647</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>426</v>
+        <v>695</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>379</v>
+        <v>648</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>427</v>
+        <v>696</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>7.64</v>
@@ -5879,7 +9484,7 @@
         <v>4.5</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J22" s="5" t="str">
         <f aca="false">IF(G22&gt;=H22,"PASS","FAIL")</f>
@@ -5888,22 +9493,22 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>381</v>
+        <v>650</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>384</v>
+        <v>653</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>383</v>
+        <v>652</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>428</v>
+        <v>697</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G23" s="10" t="n">
         <v>7.18</v>
@@ -5912,7 +9517,7 @@
         <v>4.5</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J23" s="6" t="str">
         <f aca="false">IF(G23&gt;=H23,"PASS","FAIL")</f>
@@ -5921,22 +9526,22 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>385</v>
+        <v>654</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>429</v>
+        <v>698</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>386</v>
+        <v>655</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>430</v>
+        <v>699</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>7.73</v>
@@ -5945,7 +9550,7 @@
         <v>4.5</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J24" s="5" t="str">
         <f aca="false">IF(G24&gt;=H24,"PASS","FAIL")</f>
@@ -5954,22 +9559,22 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>388</v>
+        <v>657</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>391</v>
+        <v>660</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>390</v>
+        <v>659</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>431</v>
+        <v>700</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G25" s="10" t="n">
         <v>7.28</v>
@@ -5978,7 +9583,7 @@
         <v>4.5</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J25" s="6" t="str">
         <f aca="false">IF(G25&gt;=H25,"PASS","FAIL")</f>
@@ -5987,22 +9592,22 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>392</v>
+        <v>661</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>432</v>
+        <v>701</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>393</v>
+        <v>662</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>433</v>
+        <v>702</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>7.72</v>
@@ -6011,7 +9616,7 @@
         <v>4.5</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J26" s="5" t="str">
         <f aca="false">IF(G26&gt;=H26,"PASS","FAIL")</f>
@@ -6020,22 +9625,22 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>396</v>
+        <v>665</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>434</v>
+        <v>703</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>398</v>
+        <v>667</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>435</v>
+        <v>704</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G27" s="10" t="n">
         <v>7.24</v>
@@ -6044,7 +9649,7 @@
         <v>4.5</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J27" s="6" t="str">
         <f aca="false">IF(G27&gt;=H27,"PASS","FAIL")</f>
@@ -6053,22 +9658,22 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>400</v>
+        <v>669</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>436</v>
+        <v>705</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>402</v>
+        <v>671</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>437</v>
+        <v>706</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G28" s="9" t="n">
         <v>14.34</v>
@@ -6077,7 +9682,7 @@
         <v>4.5</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J28" s="5" t="str">
         <f aca="false">IF(G28&gt;=H28,"PASS","FAIL")</f>
@@ -6086,22 +9691,22 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>404</v>
+        <v>673</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>438</v>
+        <v>707</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>402</v>
+        <v>671</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>437</v>
+        <v>706</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G29" s="10" t="n">
         <v>10.87</v>
@@ -6110,7 +9715,7 @@
         <v>4.5</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J29" s="6" t="str">
         <f aca="false">IF(G29&gt;=H29,"PASS","FAIL")</f>
@@ -6119,22 +9724,22 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>400</v>
+        <v>669</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>436</v>
+        <v>705</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>406</v>
+        <v>675</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>437</v>
+        <v>706</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>14.34</v>
@@ -6143,7 +9748,7 @@
         <v>4.5</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J30" s="5" t="str">
         <f aca="false">IF(G30&gt;=H30,"PASS","FAIL")</f>
@@ -6152,22 +9757,22 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>400</v>
+        <v>669</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>436</v>
+        <v>705</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>407</v>
+        <v>676</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>439</v>
+        <v>708</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G31" s="10" t="n">
         <v>13.16</v>
@@ -6176,7 +9781,7 @@
         <v>4.5</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J31" s="6" t="str">
         <f aca="false">IF(G31&gt;=H31,"PASS","FAIL")</f>
@@ -6185,22 +9790,22 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>400</v>
+        <v>669</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>436</v>
+        <v>705</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>409</v>
+        <v>678</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>440</v>
+        <v>709</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>12.32</v>
@@ -6209,7 +9814,7 @@
         <v>4.5</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J32" s="5" t="str">
         <f aca="false">IF(G32&gt;=H32,"PASS","FAIL")</f>
@@ -6218,22 +9823,22 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>400</v>
+        <v>669</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>436</v>
+        <v>705</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>411</v>
+        <v>680</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>441</v>
+        <v>710</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G33" s="10" t="n">
         <v>11.57</v>
@@ -6242,7 +9847,7 @@
         <v>4.5</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J33" s="6" t="str">
         <f aca="false">IF(G33&gt;=H33,"PASS","FAIL")</f>
@@ -6251,22 +9856,22 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>400</v>
+        <v>669</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>436</v>
+        <v>705</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>413</v>
+        <v>682</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>442</v>
+        <v>711</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>11.27</v>
@@ -6275,7 +9880,7 @@
         <v>4.5</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J34" s="5" t="str">
         <f aca="false">IF(G34&gt;=H34,"PASS","FAIL")</f>
@@ -6284,22 +9889,22 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>415</v>
+        <v>684</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>418</v>
+        <v>687</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>417</v>
+        <v>686</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>436</v>
+        <v>705</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>372</v>
+        <v>641</v>
       </c>
       <c r="G35" s="10" t="n">
         <v>10.14</v>
@@ -6308,7 +9913,7 @@
         <v>4.5</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J35" s="6" t="str">
         <f aca="false">IF(G35&gt;=H35,"PASS","FAIL")</f>
@@ -6317,22 +9922,22 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>419</v>
+        <v>688</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>443</v>
+        <v>712</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>402</v>
+        <v>671</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>437</v>
+        <v>706</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>421</v>
+        <v>690</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>5.82</v>
@@ -6341,7 +9946,7 @@
         <v>3</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J36" s="5" t="str">
         <f aca="false">IF(G36&gt;=H36,"PASS","FAIL")</f>
@@ -6350,22 +9955,22 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>370</v>
+        <v>639</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>424</v>
+        <v>693</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>402</v>
+        <v>671</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>437</v>
+        <v>706</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>421</v>
+        <v>690</v>
       </c>
       <c r="G37" s="10" t="n">
         <v>10.92</v>
@@ -6374,7 +9979,7 @@
         <v>3</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J37" s="6" t="str">
         <f aca="false">IF(G37&gt;=H37,"PASS","FAIL")</f>
@@ -6383,22 +9988,22 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>400</v>
+        <v>669</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>436</v>
+        <v>705</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>444</v>
+        <v>713</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>437</v>
+        <v>706</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>445</v>
+        <v>714</v>
       </c>
       <c r="G38" s="9" t="n">
         <v>14.34</v>
@@ -6407,7 +10012,7 @@
         <v>4.5</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J38" s="5" t="str">
         <f aca="false">IF(G38&gt;=H38,"PASS","FAIL")</f>
@@ -6416,22 +10021,22 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>400</v>
+        <v>669</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>436</v>
+        <v>705</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>446</v>
+        <v>715</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>439</v>
+        <v>708</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>445</v>
+        <v>714</v>
       </c>
       <c r="G39" s="10" t="n">
         <v>13.16</v>
@@ -6440,7 +10045,7 @@
         <v>4.5</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J39" s="6" t="str">
         <f aca="false">IF(G39&gt;=H39,"PASS","FAIL")</f>
@@ -6449,22 +10054,22 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>400</v>
+        <v>669</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>436</v>
+        <v>705</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>447</v>
+        <v>716</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>440</v>
+        <v>709</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>445</v>
+        <v>714</v>
       </c>
       <c r="G40" s="9" t="n">
         <v>12.32</v>
@@ -6473,7 +10078,7 @@
         <v>4.5</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J40" s="5" t="str">
         <f aca="false">IF(G40&gt;=H40,"PASS","FAIL")</f>
@@ -6482,22 +10087,22 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>400</v>
+        <v>669</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>436</v>
+        <v>705</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>448</v>
+        <v>717</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>441</v>
+        <v>710</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>445</v>
+        <v>714</v>
       </c>
       <c r="G41" s="10" t="n">
         <v>11.57</v>
@@ -6506,7 +10111,7 @@
         <v>4.5</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J41" s="6" t="str">
         <f aca="false">IF(G41&gt;=H41,"PASS","FAIL")</f>
@@ -6515,22 +10120,22 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>400</v>
+        <v>669</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>436</v>
+        <v>705</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>449</v>
+        <v>718</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>442</v>
+        <v>711</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>445</v>
+        <v>714</v>
       </c>
       <c r="G42" s="9" t="n">
         <v>11.27</v>
@@ -6539,7 +10144,7 @@
         <v>4.5</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J42" s="5" t="str">
         <f aca="false">IF(G42&gt;=H42,"PASS","FAIL")</f>
@@ -6548,22 +10153,22 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>422</v>
+        <v>691</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>400</v>
+        <v>669</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>436</v>
+        <v>705</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>450</v>
+        <v>719</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>451</v>
+        <v>720</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>445</v>
+        <v>714</v>
       </c>
       <c r="G43" s="10" t="n">
         <v>10.71</v>
@@ -6572,7 +10177,7 @@
         <v>4.5</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>373</v>
+        <v>642</v>
       </c>
       <c r="J43" s="6" t="str">
         <f aca="false">IF(G43&gt;=H43,"PASS","FAIL")</f>
@@ -6586,7 +10191,7 @@
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
-        <v>452</v>
+        <v>721</v>
       </c>
       <c r="G44" s="9" t="n">
         <f aca="false">MIN(G2:G43)</f>
@@ -6594,7 +10199,7 @@
       </c>
       <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
-        <v>453</v>
+        <v>722</v>
       </c>
       <c r="J44" s="5" t="str">
         <f aca="false">IF(COUNTIF(J2:J43,"FAIL")=0,"ALL PASS","FAILURES PRESENT")</f>
@@ -6608,15 +10213,15 @@
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6" t="s">
-        <v>454</v>
+        <v>723</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>455</v>
+        <v>724</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
       <c r="J45" s="6" t="s">
-        <v>456</v>
+        <v>725</v>
       </c>
     </row>
   </sheetData>
